--- a/artfynd/A 18734-2024 artfynd.xlsx
+++ b/artfynd/A 18734-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129721550</v>
       </c>
       <c r="B2" t="n">
-        <v>58368</v>
+        <v>58369</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 18734-2024 artfynd.xlsx
+++ b/artfynd/A 18734-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129721550</v>
       </c>
       <c r="B2" t="n">
-        <v>58369</v>
+        <v>58372</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 18734-2024 artfynd.xlsx
+++ b/artfynd/A 18734-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129721550</v>
       </c>
       <c r="B2" t="n">
-        <v>58372</v>
+        <v>58375</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 18734-2024 artfynd.xlsx
+++ b/artfynd/A 18734-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129721550</v>
       </c>
       <c r="B2" t="n">
-        <v>58375</v>
+        <v>58376</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 18734-2024 artfynd.xlsx
+++ b/artfynd/A 18734-2024 artfynd.xlsx
@@ -678,11 +678,11 @@
         <v>129721550</v>
       </c>
       <c r="B2" t="n">
-        <v>58376</v>
+        <v>58592</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
